--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_037_Macquarie_Isl_Australia.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_037_Macquarie_Isl_Australia.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R36e73563af234665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R87a9ca13b57541d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rdb5365f2db604213"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6cdbe2df3fff4b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Ra68e9cc62c4b49fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R398da5484dd04217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra838f5f9c3d947b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re578c826057e4b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb1ded8982ef04f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rcebd33e329304b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbe80736f88624d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8019f642fe1c42d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ037CommercialTable" displayName="EEZ037CommercialTable" ref="A1:O2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O2"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ037CommercialTable" displayName="EEZ037CommercialTable" ref="A1:E2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E2"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ037FunctionalTable" displayName="EEZ037FunctionalTable" ref="A1:O2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O2"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ037FunctionalTable" displayName="EEZ037FunctionalTable" ref="A1:E2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E2"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ037ValidationTable" displayName="EEZ037ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ037ValidationTable" displayName="EEZ037ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -761,7 +715,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de0ef57c1af4d10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R285c8343ed964ac2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -771,20 +725,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -792,120 +736,41 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>434.33</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.96</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>912.0108393559096</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>434.33</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>912.0108393559096</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$2,A2,'Species'!$U$2:$U$2))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>396113.66785745224</x:v>
       </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.96</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>912.0108393559096</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>396113.66785745224</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G2">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O2">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca59ad28afca4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R275e39bccf9f4d4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -915,20 +780,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -936,120 +791,41 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>434.33</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.96</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>912.0108393559096</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>434.33</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>912.0108393559096</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$2,A2,'Species'!$U$2:$U$2))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>396113.66785745224</x:v>
       </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.96</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>912.0108393559096</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>396113.66785745224</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G2">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O2">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8176e9af11a476e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f92a89a4b5c4343"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1224,7 +1000,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -1376,9 +1152,9 @@
         <x:v>EEZ_037</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -1390,47 +1166,19 @@
         <x:v>EEZ_037</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_037</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_037</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3b30ea312864906"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf80c055111234d51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1477,7 +1225,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
